--- a/diseases/d001/2005-2009.xlsx
+++ b/diseases/d001/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1605,9 +1599,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1901,9 +1892,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2197,9 +2185,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2493,9 +2478,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2789,9 +2771,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3085,9 +3064,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3381,9 +3357,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3677,9 +3650,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -3973,9 +3943,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4269,9 +4236,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4565,9 +4529,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -4861,9 +4822,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -5257,9 +5215,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5553,9 +5508,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5849,9 +5801,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6145,9 +6094,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6441,9 +6387,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6737,9 +6680,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -7033,9 +6973,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7329,9 +7266,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -7625,9 +7559,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -7921,9 +7852,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8217,9 +8145,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8513,9 +8438,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -8957,9 +8879,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -9353,9 +9272,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -9797,9 +9713,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -10241,9 +10154,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -10685,9 +10595,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -11129,9 +11036,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -11573,9 +11477,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -11869,9 +11770,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -12313,9 +12211,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -12609,9 +12504,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -13053,9 +12945,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -13497,9 +13386,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -13941,9 +13827,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -14385,9 +14268,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -14781,9 +14661,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -15225,9 +15102,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -15669,9 +15543,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -16113,9 +15984,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -16557,9 +16425,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -17001,9 +16866,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -17445,9 +17307,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -17889,9 +17748,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -18333,9 +18189,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -18629,9 +18482,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -18925,9 +18775,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -19369,9 +19216,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -19813,9 +19657,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -20209,9 +20050,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -20653,9 +20491,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -21097,9 +20932,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -21541,9 +21373,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -21837,9 +21666,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -22281,9 +22107,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -22725,9 +22548,6 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
@@ -23169,9 +22989,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -23613,9 +23430,6 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
@@ -24057,9 +23871,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -24501,9 +24312,6 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
@@ -24943,9 +24751,6 @@
         <v>0</v>
       </c>
       <c r="O162" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q162" t="n">
         <v>0</v>
       </c>
       <c r="R162" t="n">
